--- a/docs/WEEKLY_REPORT.xlsx
+++ b/docs/WEEKLY_REPORT.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Project\scan-captcha-project\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B516EC11-5730-44CA-A4B0-EE903293C025}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2910EF25-3811-4C99-B597-EA0E8948B932}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="85">
   <si>
     <t>WEEK</t>
   </si>
@@ -32,31 +32,24 @@
     <t>DESCRIPTION</t>
   </si>
   <si>
-    <t>16/10 -&gt;22/10</t>
+    <t>23/10 -&gt;29/10</t>
   </si>
   <si>
     <t>SCRAPING</t>
   </si>
   <si>
-    <t>1. Captcha OCR - 107,364 labelled samples over 20 invoice portals
-- Usable : 12 models / 66,966 samples (10 of them 94-100%)
-- Trained this week : GDT login 13,757 samples -&gt; 87.3% (54 epochs, ~40h) ; Thai Son 13,306 -&gt; 89.2%, first working model for that portal
-- Re-training : VN-Invoice 11,632 samples - labels were wrong on upper/lower case, corrected this week ; Thai Son at higher resolution
-- Not usable yet : 8 portals / 40,398 samples - need more samples or label clean-up
-2. Changed how invoices are pulled from the tax portal : take the whole list first (one "Export Excel" request per invoice type), then download each XML from that list (Done 10/20)
--&gt; the old way paged through the API while downloading, so invoices could be missed when the paging shifted
-3. Invoice email reader (IMAP, read-only, never opens a link) : 68 mails scanned, 50 recognised as invoice mails
-- 28 attachments extracted : 17 PDF + 11 XML, including files inside .zip and forwarded .eml
-- 13 matched to invoices in the database (11 PDF + 2 XML) ; 14 were duplicates of what the tax portal already provided
-- 57 lookup links found : 16 fetched through the supplier adapters, 27 waiting for an adapter
-Current total : 1,012 invoices / 799 XML / 138 original PDFs through 11 supplier adapters
-Nextweek:
--&gt; Retrain the VN-Invoice captcha model on the corrected labels
--&gt; Build the Thai Son (einvoice.vn) PDF adapter - its captcha model is ready
--&gt; 232 invoices still have no PDF source : add adapters for the largest suppliers</t>
+    <t>16/10 -&gt;22/10</t>
   </si>
   <si>
     <t>SETUP SEVER</t>
+  </si>
+  <si>
+    <t>- New server for the scraping job : Python 3.13 + dependencies installed (Done 10/21):
+  Souce code: (192.168.60.13), DB:(192.168.60.121), link:(https://we-scraping.wetax.com.vn/login)
+- Scheduled task can now run while logged off, needed on a server with no interactive session
+Nextweek:
+-&gt; Training template countine
+-&gt; Checking the schedule</t>
   </si>
   <si>
     <t>DATE</t>
@@ -292,12 +285,151 @@
     <t>Join meeting with BIDV PICs (WeCMS, WeBill)</t>
   </si>
   <si>
-    <t>- New server for the scraping job : Python 3.13 + dependencies installed (Done 10/21):
-  Souce code: (192.168.60.13), DB:(192.168.60.121), link:(https://we-scraping.wetax.com.vn/login)
-- Scheduled task can now run while logged off, needed on a server with no interactive session
-Nextweek:
--&gt; Training template countine
--&gt; Checking the schedule</t>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Inter"/>
+      </rPr>
+      <t xml:space="preserve">1. Captcha: 15/24 done, 9 in training
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Inter"/>
+      </rPr>
+      <t xml:space="preserve">- In training: ASIA, VN-Invoice, SmartSign, PA Viet Nam, VNISC, Bitware, VDSG, Lac Viet, public service
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Inter"/>
+      </rPr>
+      <t xml:space="preserve">2. Lookup links: 27/136 suppliers done
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Inter"/>
+      </rPr>
+      <t xml:space="preserve">- Remaining 107: 48 ready, 61 not done 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Inter"/>
+      </rPr>
+      <t xml:space="preserve">3. Email: 32/136 suppliers
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Inter"/>
+      </rPr>
+      <t xml:space="preserve">- Remaining 104: 44 ready, 60 not done 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Inter"/>
+      </rPr>
+      <t xml:space="preserve">Next week:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Inter"/>
+      </rPr>
+      <t xml:space="preserve"> - Check the site design from Ms. Tuyen.
+ - Check the lookup link and email for invoice retrieval.
+ - Captcha training is not sufficient if the captcha results are not satisfactory.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Inter"/>
+      </rPr>
+      <t>1. Captcha OCR - 107,364 labelled samples over 20 invoice portals</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Inter"/>
+      </rPr>
+      <t xml:space="preserve">
+- Usable : 12 models / 66,966 samples (10 of them 94-100%)
+- Trained this week : GDT login 13,757 samples -&gt; 87.3% (54 epochs, ~40h) ; Thai Son 13,306 -&gt; 89.2%, first working model for that portal
+- Re-training : VN-Invoice 11,632 samples - labels were wrong on upper/lower case, corrected this week ; Thai Son at higher resolution
+- Not usable yet : 8 portals / 40,398 samples - need more samples or label clean-up
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Inter"/>
+      </rPr>
+      <t>2. Changed how invoices are pulled from the tax portal : take the whole list first (one "Export Excel" request per invoice type), then download each XML from that list (Done 10/20)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Inter"/>
+      </rPr>
+      <t xml:space="preserve">
+-&gt; the old way paged through the API while downloading, so invoices could be missed when the paging shifted
+3. Invoice email reader (IMAP, read-only, never opens a link) : 68 mails scanned, 50 recognised as invoice mails
+- 28 attachments extracted : 17 PDF + 11 XML, including files inside .zip and forwarded .eml
+- 13 matched to invoices in the database (11 PDF + 2 XML) ; 14 were duplicates of what the tax portal already provided
+- 57 lookup links found : 16 fetched through the supplier adapters, 27 waiting for an adapter
+Current total : 1,012 invoices / 799 XML / 138 original PDFs through 11 supplier adapters
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Inter"/>
+      </rPr>
+      <t>Nextweek:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Inter"/>
+      </rPr>
+      <t xml:space="preserve">
+-&gt; Retrain the VN-Invoice captcha model on the corrected labels
+-&gt; Build the Thai Son (einvoice.vn) PDF adapter - its captcha model is ready
+-&gt; 232 invoices still have no PDF source : add adapters for the largest suppliers</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -460,7 +592,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -561,11 +693,24 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -689,21 +834,6 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -716,7 +846,25 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -947,7 +1095,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A1" s="58" t="s">
+      <c r="A1" s="51" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
@@ -979,15 +1127,15 @@
       <c r="X1" s="2"/>
       <c r="Y1" s="2"/>
     </row>
-    <row r="2" spans="1:25" ht="268" customHeight="1">
-      <c r="A2" s="59" t="s">
+    <row r="2" spans="1:25" ht="147" customHeight="1">
+      <c r="A2" s="52" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="57" t="s">
+      <c r="B2" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="49" t="s">
-        <v>5</v>
+      <c r="C2" s="53" t="s">
+        <v>83</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
@@ -1012,13 +1160,15 @@
       <c r="X2" s="3"/>
       <c r="Y2" s="3"/>
     </row>
-    <row r="3" spans="1:25" ht="77.5" customHeight="1">
-      <c r="A3" s="60"/>
-      <c r="B3" s="57" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="56" t="s">
-        <v>82</v>
+    <row r="3" spans="1:25" ht="268" customHeight="1">
+      <c r="A3" s="54" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="50" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="53" t="s">
+        <v>84</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
@@ -1043,10 +1193,14 @@
       <c r="X3" s="3"/>
       <c r="Y3" s="3"/>
     </row>
-    <row r="4" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
+    <row r="4" spans="1:25" ht="77.5" customHeight="1">
+      <c r="A4" s="55"/>
+      <c r="B4" s="50" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="49" t="s">
+        <v>7</v>
+      </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
@@ -7143,7 +7297,7 @@
     <row r="901" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="A3:A4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -7167,19 +7321,19 @@
     <row r="1" spans="1:26" ht="15.75" customHeight="1">
       <c r="A1" s="4"/>
       <c r="B1" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G1" s="6"/>
       <c r="H1" s="6"/>
@@ -7205,7 +7359,7 @@
     <row r="2" spans="1:26" ht="15.75" customHeight="1">
       <c r="A2" s="7"/>
       <c r="B2" s="8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C2" s="9"/>
       <c r="D2" s="10"/>
@@ -7686,16 +7840,16 @@
         <v>45968</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D19" s="16" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E19" s="17" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F19" s="15" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G19" s="6"/>
       <c r="H19" s="6"/>
@@ -7722,16 +7876,16 @@
       <c r="A20" s="13"/>
       <c r="B20" s="14"/>
       <c r="C20" s="15" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D20" s="16" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E20" s="17" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F20" s="15" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G20" s="6"/>
       <c r="H20" s="6"/>
@@ -7760,16 +7914,16 @@
         <v>45998</v>
       </c>
       <c r="C21" s="15" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D21" s="16" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E21" s="17" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F21" s="15" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G21" s="6"/>
       <c r="H21" s="6"/>
@@ -7796,14 +7950,14 @@
       <c r="A22" s="13"/>
       <c r="B22" s="14"/>
       <c r="C22" s="15" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D22" s="16" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E22" s="18"/>
       <c r="F22" s="15" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G22" s="6"/>
       <c r="H22" s="6"/>
@@ -7829,19 +7983,19 @@
     <row r="23" spans="1:26" ht="15.75" customHeight="1">
       <c r="A23" s="13"/>
       <c r="B23" s="19" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C23" s="15" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D23" s="16" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E23" s="17" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F23" s="15" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G23" s="6"/>
       <c r="H23" s="6"/>
@@ -7868,16 +8022,16 @@
       <c r="A24" s="13"/>
       <c r="B24" s="14"/>
       <c r="C24" s="15" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D24" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="E24" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="F24" s="15" t="s">
         <v>27</v>
-      </c>
-      <c r="E24" s="17" t="s">
-        <v>28</v>
-      </c>
-      <c r="F24" s="15" t="s">
-        <v>26</v>
       </c>
       <c r="G24" s="6"/>
       <c r="H24" s="6"/>
@@ -7904,16 +8058,16 @@
       <c r="A25" s="13"/>
       <c r="B25" s="14"/>
       <c r="C25" s="15" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D25" s="16" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E25" s="17" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F25" s="15" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G25" s="6"/>
       <c r="H25" s="6"/>
@@ -7939,19 +8093,19 @@
     <row r="26" spans="1:26" ht="15.75" customHeight="1">
       <c r="A26" s="13"/>
       <c r="B26" s="19" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C26" s="15" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D26" s="16" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E26" s="17" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F26" s="15" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G26" s="6"/>
       <c r="H26" s="6"/>
@@ -7978,16 +8132,16 @@
       <c r="A27" s="13"/>
       <c r="B27" s="14"/>
       <c r="C27" s="15" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D27" s="16" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E27" s="17" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F27" s="15" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G27" s="6"/>
       <c r="H27" s="6"/>
@@ -8014,16 +8168,16 @@
       <c r="A28" s="13"/>
       <c r="B28" s="14"/>
       <c r="C28" s="15" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D28" s="16" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E28" s="16" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F28" s="15" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G28" s="6"/>
       <c r="H28" s="6"/>
@@ -8050,7 +8204,7 @@
       <c r="A29" s="13"/>
       <c r="B29" s="14"/>
       <c r="C29" s="15" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D29" s="16"/>
       <c r="E29" s="16"/>
@@ -8079,19 +8233,19 @@
     <row r="30" spans="1:26" ht="15.75" customHeight="1">
       <c r="A30" s="13"/>
       <c r="B30" s="19" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C30" s="15" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D30" s="16" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E30" s="20" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F30" s="15" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G30" s="6"/>
       <c r="H30" s="6"/>
@@ -8118,13 +8272,13 @@
       <c r="A31" s="13"/>
       <c r="B31" s="14"/>
       <c r="C31" s="15" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D31" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="E31" s="20" t="s">
         <v>41</v>
-      </c>
-      <c r="E31" s="20" t="s">
-        <v>40</v>
       </c>
       <c r="F31" s="15"/>
       <c r="G31" s="6"/>
@@ -8151,16 +8305,16 @@
     <row r="32" spans="1:26" ht="15.75" customHeight="1">
       <c r="A32" s="13"/>
       <c r="B32" s="19" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C32" s="15" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D32" s="16" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E32" s="20" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F32" s="15"/>
       <c r="G32" s="6"/>
@@ -8188,10 +8342,10 @@
       <c r="A33" s="13"/>
       <c r="B33" s="14"/>
       <c r="C33" s="15" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D33" s="16" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E33" s="18"/>
       <c r="F33" s="15"/>
@@ -8219,16 +8373,16 @@
     <row r="34" spans="1:26" ht="15.75" customHeight="1">
       <c r="A34" s="13"/>
       <c r="B34" s="21" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C34" s="15" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D34" s="16" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E34" s="22" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F34" s="23"/>
       <c r="G34" s="6"/>
@@ -8257,7 +8411,7 @@
       <c r="B35" s="24"/>
       <c r="C35" s="15"/>
       <c r="D35" s="16" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E35" s="25"/>
       <c r="F35" s="23"/>
@@ -8283,23 +8437,23 @@
       <c r="Z35" s="6"/>
     </row>
     <row r="36" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A36" s="53" t="s">
-        <v>49</v>
-      </c>
-      <c r="B36" s="52">
+      <c r="A36" s="59" t="s">
+        <v>50</v>
+      </c>
+      <c r="B36" s="56">
         <v>45845</v>
       </c>
       <c r="C36" s="23" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D36" s="26" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E36" s="22" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F36" s="23" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G36" s="6"/>
       <c r="H36" s="6"/>
@@ -8323,17 +8477,17 @@
       <c r="Z36" s="6"/>
     </row>
     <row r="37" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A37" s="54"/>
-      <c r="B37" s="50"/>
+      <c r="A37" s="60"/>
+      <c r="B37" s="57"/>
       <c r="C37" s="23" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D37" s="26" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E37" s="25"/>
       <c r="F37" s="23" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G37" s="6"/>
       <c r="H37" s="6"/>
@@ -8357,17 +8511,17 @@
       <c r="Z37" s="6"/>
     </row>
     <row r="38" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A38" s="54"/>
-      <c r="B38" s="50"/>
+      <c r="A38" s="60"/>
+      <c r="B38" s="57"/>
       <c r="C38" s="23" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D38" s="26" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E38" s="25"/>
       <c r="F38" s="23" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G38" s="6"/>
       <c r="H38" s="6"/>
@@ -8391,17 +8545,17 @@
       <c r="Z38" s="6"/>
     </row>
     <row r="39" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A39" s="54"/>
-      <c r="B39" s="51"/>
+      <c r="A39" s="60"/>
+      <c r="B39" s="58"/>
       <c r="C39" s="23" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D39" s="26" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E39" s="25"/>
       <c r="F39" s="23" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G39" s="6"/>
       <c r="H39" s="6"/>
@@ -8425,19 +8579,19 @@
       <c r="Z39" s="6"/>
     </row>
     <row r="40" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A40" s="54"/>
-      <c r="B40" s="52">
+      <c r="A40" s="60"/>
+      <c r="B40" s="56">
         <v>45876</v>
       </c>
       <c r="C40" s="23" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D40" s="26" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E40" s="25"/>
       <c r="F40" s="23" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G40" s="6"/>
       <c r="H40" s="6"/>
@@ -8461,19 +8615,19 @@
       <c r="Z40" s="6"/>
     </row>
     <row r="41" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A41" s="54"/>
-      <c r="B41" s="50"/>
+      <c r="A41" s="60"/>
+      <c r="B41" s="57"/>
       <c r="C41" s="23" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D41" s="26" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E41" s="22" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F41" s="23" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G41" s="6"/>
       <c r="H41" s="6"/>
@@ -8497,17 +8651,17 @@
       <c r="Z41" s="6"/>
     </row>
     <row r="42" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A42" s="54"/>
-      <c r="B42" s="50"/>
+      <c r="A42" s="60"/>
+      <c r="B42" s="57"/>
       <c r="C42" s="23" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D42" s="26" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E42" s="25"/>
       <c r="F42" s="23" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G42" s="6"/>
       <c r="H42" s="6"/>
@@ -8531,19 +8685,19 @@
       <c r="Z42" s="6"/>
     </row>
     <row r="43" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A43" s="54"/>
-      <c r="B43" s="50"/>
+      <c r="A43" s="60"/>
+      <c r="B43" s="57"/>
       <c r="C43" s="23" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D43" s="26" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E43" s="27" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F43" s="28" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G43" s="6"/>
       <c r="H43" s="6"/>
@@ -8567,19 +8721,19 @@
       <c r="Z43" s="6"/>
     </row>
     <row r="44" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A44" s="54"/>
-      <c r="B44" s="50"/>
+      <c r="A44" s="60"/>
+      <c r="B44" s="57"/>
       <c r="C44" s="21" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D44" s="29" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E44" s="25" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F44" s="30" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G44" s="6"/>
       <c r="H44" s="6"/>
@@ -8603,17 +8757,17 @@
       <c r="Z44" s="6"/>
     </row>
     <row r="45" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A45" s="54"/>
-      <c r="B45" s="51"/>
+      <c r="A45" s="60"/>
+      <c r="B45" s="58"/>
       <c r="C45" s="23" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D45" s="26" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E45" s="25"/>
       <c r="F45" s="23" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G45" s="6"/>
       <c r="H45" s="6"/>
@@ -8637,19 +8791,19 @@
       <c r="Z45" s="6"/>
     </row>
     <row r="46" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A46" s="54"/>
-      <c r="B46" s="52">
+      <c r="A46" s="60"/>
+      <c r="B46" s="56">
         <v>45907</v>
       </c>
       <c r="C46" s="23" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D46" s="26" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E46" s="25"/>
       <c r="F46" s="23" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G46" s="6"/>
       <c r="H46" s="6"/>
@@ -8673,19 +8827,19 @@
       <c r="Z46" s="6"/>
     </row>
     <row r="47" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A47" s="54"/>
-      <c r="B47" s="51"/>
+      <c r="A47" s="60"/>
+      <c r="B47" s="58"/>
       <c r="C47" s="23" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D47" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E47" s="31" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F47" s="28" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G47" s="6"/>
       <c r="H47" s="6"/>
@@ -8709,21 +8863,21 @@
       <c r="Z47" s="6"/>
     </row>
     <row r="48" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A48" s="54"/>
-      <c r="B48" s="52">
+      <c r="A48" s="60"/>
+      <c r="B48" s="56">
         <v>45937</v>
       </c>
       <c r="C48" s="32" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D48" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E48" s="31" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F48" s="32" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G48" s="6"/>
       <c r="H48" s="6"/>
@@ -8747,17 +8901,17 @@
       <c r="Z48" s="6"/>
     </row>
     <row r="49" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A49" s="54"/>
-      <c r="B49" s="51"/>
+      <c r="A49" s="60"/>
+      <c r="B49" s="58"/>
       <c r="C49" s="32" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D49" s="25" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E49" s="25"/>
       <c r="F49" s="32" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G49" s="6"/>
       <c r="H49" s="6"/>
@@ -8781,15 +8935,15 @@
       <c r="Z49" s="6"/>
     </row>
     <row r="50" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A50" s="53" t="s">
-        <v>69</v>
-      </c>
-      <c r="B50" s="55"/>
+      <c r="A50" s="59" t="s">
+        <v>70</v>
+      </c>
+      <c r="B50" s="61"/>
       <c r="C50" s="32" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D50" s="25" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E50" s="25"/>
       <c r="F50" s="32"/>
@@ -8815,13 +8969,13 @@
       <c r="Z50" s="6"/>
     </row>
     <row r="51" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A51" s="54"/>
-      <c r="B51" s="50"/>
+      <c r="A51" s="60"/>
+      <c r="B51" s="57"/>
       <c r="C51" s="32" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D51" s="25" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E51" s="25"/>
       <c r="F51" s="32"/>
@@ -8847,13 +9001,13 @@
       <c r="Z51" s="6"/>
     </row>
     <row r="52" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A52" s="54"/>
-      <c r="B52" s="51"/>
+      <c r="A52" s="60"/>
+      <c r="B52" s="58"/>
       <c r="C52" s="32" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D52" s="26" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E52" s="25"/>
       <c r="F52" s="32"/>
@@ -8884,13 +9038,13 @@
         <v>45664</v>
       </c>
       <c r="C53" s="35" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D53" s="36" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E53" s="37" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F53" s="38"/>
       <c r="G53" s="6"/>
@@ -8920,13 +9074,13 @@
         <v>45695</v>
       </c>
       <c r="C54" s="41" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D54" s="42" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E54" s="43" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F54" s="36"/>
       <c r="G54" s="6"/>
@@ -8956,13 +9110,13 @@
         <v>45695</v>
       </c>
       <c r="C55" s="35" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D55" s="36" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E55" s="36" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F55" s="36"/>
       <c r="G55" s="6"/>
@@ -8992,13 +9146,13 @@
         <v>45695</v>
       </c>
       <c r="C56" s="41" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D56" s="45" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E56" s="45" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F56" s="45"/>
       <c r="G56" s="6"/>
@@ -9028,13 +9182,13 @@
         <v>45723</v>
       </c>
       <c r="C57" s="35" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D57" s="46" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E57" s="37" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F57" s="38"/>
       <c r="G57" s="47"/>
@@ -9064,13 +9218,13 @@
         <v>45754</v>
       </c>
       <c r="C58" s="35" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D58" s="36" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E58" s="36" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F58" s="36"/>
       <c r="G58" s="6"/>
@@ -9100,10 +9254,10 @@
         <v>45755</v>
       </c>
       <c r="C59" s="48" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D59" s="38" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E59" s="38"/>
       <c r="F59" s="38"/>
